--- a/Produkty/989-50071989.xlsx
+++ b/Produkty/989-50071989.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:M9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,13 +430,22 @@
       <c r="J1" t="str">
         <v>Stanowisko</v>
       </c>
+      <c r="K1" t="str">
+        <v>Ilość</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Grupa</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Priorytet</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>1940x60x28-989</v>
+        <v>1940x60x28</v>
       </c>
       <c r="C2" t="str">
         <v>1940</v>
@@ -462,13 +471,22 @@
       <c r="J2" t="str">
         <v>3</v>
       </c>
+      <c r="K2" t="str">
+        <v>2</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>1840x60x28-989</v>
+        <v>1840x60x28</v>
       </c>
       <c r="C3" t="str">
         <v>1840</v>
@@ -494,13 +512,22 @@
       <c r="J3" t="str">
         <v>3</v>
       </c>
+      <c r="K3" t="str">
+        <v>1</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>1770x60x28-989</v>
+        <v>1770x60x28</v>
       </c>
       <c r="C4" t="str">
         <v>1770</v>
@@ -526,13 +553,22 @@
       <c r="J4" t="str">
         <v>3</v>
       </c>
+      <c r="K4" t="str">
+        <v>1</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>675x60x28-989</v>
+        <v>675x60x28</v>
       </c>
       <c r="C5" t="str">
         <v>675</v>
@@ -558,13 +594,22 @@
       <c r="J5" t="str">
         <v>2</v>
       </c>
+      <c r="K5" t="str">
+        <v>1</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v/>
       </c>
       <c r="B6" t="str">
-        <v>800x80x28-989</v>
+        <v>800x80x28</v>
       </c>
       <c r="C6" t="str">
         <v>800</v>
@@ -590,13 +635,22 @@
       <c r="J6" t="str">
         <v>2</v>
       </c>
+      <c r="K6" t="str">
+        <v>2</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v/>
       </c>
       <c r="B7" t="str">
-        <v>880x15x28-989</v>
+        <v>880x15x28</v>
       </c>
       <c r="C7" t="str">
         <v>880</v>
@@ -622,13 +676,22 @@
       <c r="J7" t="str">
         <v>2</v>
       </c>
+      <c r="K7" t="str">
+        <v>1</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v/>
       </c>
       <c r="B8" t="str">
-        <v>510x10x28-989</v>
+        <v>510x10x28</v>
       </c>
       <c r="C8" t="str">
         <v>510</v>
@@ -654,13 +717,22 @@
       <c r="J8" t="str">
         <v>2</v>
       </c>
+      <c r="K8" t="str">
+        <v>2</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v/>
       </c>
       <c r="B9" t="str">
-        <v>500x10x28-989</v>
+        <v>500x10x28</v>
       </c>
       <c r="C9" t="str">
         <v>500</v>
@@ -686,10 +758,19 @@
       <c r="J9" t="str">
         <v>2</v>
       </c>
+      <c r="K9" t="str">
+        <v>1</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M9"/>
   </ignoredErrors>
 </worksheet>
 </file>